--- a/02_加值成品/八上/八上6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-1 原子與原子模型　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上6-1 原子與原子模型　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>提出原子說(實心球)的科學家？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>湯姆森</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>正電</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>道耳頓</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>質子中子電子</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>原子說</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>發現電子的科學家？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>湯姆森</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>布丁模型</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>金箔實驗發現原子核的是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不帶電</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>拉塞福</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>查兌克</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>質子與中子</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>核在中心</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>發現中子的科學家？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>質子數</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>質子與中子</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>查兌克</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>質子</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>中子</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>原子核由什麼組成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>質子與中子</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>小很多</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>同位素</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>核心</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>帶負電的粒子是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>同位素</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>電子</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>質子</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>正電</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>核外</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>原子序等於什麼數？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>質子數</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>湯姆森</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>質子與中子</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>定元素</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>原子整體帶電嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>小很多</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>不帶電</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>正電</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>原子的三種基本粒子是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>查兌克</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>原子核</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>質子中子電子</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>三種</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>帶正電的粒子是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>質子</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>不帶電</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>質子中子電子</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>正電</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-1 原子與原子模型　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上6-1 原子與原子模型　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>質子數6的元素是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>碳</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>湯姆森</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>查兌克</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>原子序6</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>質子8中子8,質量數？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>小很多</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>8+8</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>原子核帶什麼電？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>正電</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>質子</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>原子核</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>質子</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>中子帶什麼電？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>道耳頓</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>不帶電</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>查兌克</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>拉塞福</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>決定元素種類的是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>質子數</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>查兌克</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>湯姆森</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>原子序</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>拉塞福實驗少數粒子反彈說明？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>原子核小而集中帶正電</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>原子核小而集中</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>隨新實驗證據調整,科學暫時性</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>無法解釋金箔實驗反彈</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>核存在</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>質量數=質子數+？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>查兌克</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>不帶電</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>中子數</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>總和</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>電子質量比質子？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>拉塞福</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>查兌克</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>小很多</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>約1/1836</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>質子數8的元素是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>小很多</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>氧</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>湯姆森</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>原子序8</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>原子序3質量數7的中子數？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>中子數</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>湯姆森</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>質子數=電子數,正負相消</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>7−3</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-1 原子與原子模型　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上6-1 原子與原子模型　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>原子模型為何一再修正？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>無法解釋金箔實驗反彈</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>隨新實驗證據調整,科學暫時性</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>原子核小而集中帶正電</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>質子數=電子數,正負相消</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>科學本質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>金箔實驗大多粒子直穿說明？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>無法解釋金箔實驗反彈</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>原子核小而集中帶正電</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>原子內部大部分是空的</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>質子數=電子數,正負相消</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>空曠</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>原子中性是因為？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>原子內部大部分是空的</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>原子核小而集中帶正電</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>質子數=電子數,正負相消</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>無法解釋金箔實驗反彈</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>電荷平衡</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>同元素不同中子數稱？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>中子數</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>拉塞福</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>道耳頓</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>同位素</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>質子同</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>湯姆森模型為何被推翻？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>原子核小而集中</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>隨新實驗證據調整,科學暫時性</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>原子內部大部分是空的</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>無法解釋金箔實驗反彈</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>證據</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>質子11電子11的原子帶電？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>道耳頓</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>同位素</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>質子</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>不帶電</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>原子質量主要集中在？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>原子核</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>同位素</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>湯姆森</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>質子中子</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>若失去一電子原子帶何電？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>拉塞福</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>道耳頓</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>正電</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>質子中子電子</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>陽離子</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>拉塞福金箔實驗的重要結論？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>質子數=電子數,正負相消</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>隨新實驗證據調整,科學暫時性</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>原子核小而集中帶正電</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>原子內部大部分是空的</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>核</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>中性原子質子數與電子數關係？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>原子核</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>質子與中子</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>質子中子電子</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>原子說</t>
+          <t>原子說：道耳頓提出物質是由不可分割的實心球狀原子組成，是最早的原子學說</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>布丁模型</t>
+          <t>布丁模型：湯姆森發現帶負電的電子，並提出原子像布丁一樣，正電荷均勻分布、電子鑲嵌其中的模型</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>核在中心</t>
+          <t>核在中心：拉塞福用α粒子撞擊金箔，發現原子中心有一個體積小、帶正電且集中質量的原子核</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>中子</t>
+          <t>中子：查兌克發現原子核中除了帶正電的質子外，還有不帶電的中子</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>核心</t>
+          <t>核心：原子中心的原子核是由帶正電的質子和不帶電的中子組成的</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>核外</t>
+          <t>核外：電子帶負電，分布在原子核外圍的空間中繞核運動</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>定元素</t>
+          <t>定元素：原子序等於原子核內的質子數，質子數決定了是哪一種元素</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>中性：原子中質子數(正電)和電子數(負電)相等，正負電荷互相抵消，所以整體不帶電，呈電中性</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>三種</t>
+          <t>三種：組成原子的三種基本粒子是質子、中子、電子</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>正電</t>
+          <t>正電：原子中的質子帶正電，中子不帶電，電子帶負電</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>原子序6</t>
+          <t>原子序6：原子序等於質子數，質子數為6的元素就是原子序6的碳</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>8+8</t>
+          <t>8+8：質量數＝質子數加中子數，8個質子加8個中子等於16</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>質子</t>
+          <t>質子：原子核內的質子帶正電，中子不帶電，所以整個原子核帶正電</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>中性：中子是原子核中不帶電的粒子，維持原子核的穩定</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>原子序</t>
+          <t>原子序：質子數(原子序)決定了原子屬於哪一種元素，質子數不同就是不同的元素</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>核存在</t>
+          <t>核存在：極少數α粒子被大角度反彈，代表原子中心存在一個體積很小但質量集中、帶正電的原子核，才能造成這樣強烈的偏折</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>總和</t>
+          <t>總和：質量數是原子核中質子數和中子數的總和</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>約1/1836</t>
+          <t>約1/1836：電子的質量遠比質子小，大約只有質子質量的1836分之一</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>原子序8</t>
+          <t>原子序8：原子序等於質子數，質子數為8的元素就是原子序8的氧</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>7−3</t>
+          <t>7−3：中子數=質量數−質子數(原子序)，7減去3等於4個中子</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>科學本質</t>
+          <t>科學本質：每當有新的實驗證據出現，原本的原子模型若無法解釋新現象，科學家就會提出更完善的模型來修正，這正展現了科學結論具有暫時性、會隨證據演進的本質</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>空曠</t>
+          <t>空曠：大部分α粒子能直接穿過金箔而不偏折，代表原子內部除了中心極小的原子核外，絕大部分空間是空曠的</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>電荷平衡</t>
+          <t>電荷平衡：原子中帶正電的質子數和帶負電的電子數相等，正負電荷剛好互相抵消，所以整個原子呈電中性</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>質子同</t>
+          <t>質子同：同一種元素(質子數相同)，但中子數不同、質量數也不同的原子，彼此互稱同位素</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>證據</t>
+          <t>證據：湯姆森的布丁模型認為正電荷均勻分布在整個原子中，無法解釋為何金箔實驗中有極少數α粒子會被大角度反彈，因此被拉塞福的原子核模型取代</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：質子數11(正電)和電子數11(負電)相等，正負電荷互相抵消，所以這個原子不帶電</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>質子中子</t>
+          <t>質子中子：原子核內的質子和中子質量遠大於核外電子，所以原子的質量幾乎都集中在原子核</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>陽離子</t>
+          <t>陽離子：原子失去一個帶負電的電子後，正電荷(質子)比負電荷(電子)多一個，整體帶正電，形成陽離子</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>核</t>
+          <t>核：拉塞福用α粒子撞擊金箔，發現大部分粒子直接穿過、極少數大角度反彈，推論出原子中心有一個體積很小但帶正電、質量集中的原子核</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：原子不帶電(中性)時，帶正電的質子數目必須等於帶負電的電子數目，使正負電荷互相抵消</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-1_三種難度測驗卷.xlsx
@@ -728,17 +728,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>小很多</t>
+          <t>氧</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>拉塞福</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>電子</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>同位素</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>查兌克</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
           <t>同位素</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>電子</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>質子</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>正電</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>電子</t>
+          <t>原子核</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>湯姆森</t>
+          <t>中子數</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>查兌克</t>
+          <t>不帶電</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>原子核</t>
+          <t>小很多</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>電子</t>
+          <t>相等</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>道耳頓</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>不帶電</t>
+          <t>湯姆森</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>質子中子電子</t>
+          <t>電子</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1079,14 +1079,14 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>拉塞福</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
           <t>電子</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>小很多</t>
-        </is>
-      </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>16</t>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>碳</t>
+          <t>正電</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>查兌克</t>
+          <t>拉塞福</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>湯姆森</t>
+          <t>不帶電</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>原子核小而集中帶正電</t>
+          <t>原子內部大部分是空的</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>隨新實驗證據調整,科學暫時性</t>
+          <t>無法解釋金箔實驗反彈</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>無法解釋金箔實驗反彈</t>
+          <t>質子數=電子數,正負相消</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>中子數</t>
+          <t>電子</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>湯姆森</t>
+          <t>碳</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>質子數=電子數,正負相消</t>
+          <t>質子</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1835,22 +1835,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>原子內部大部分是空的</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>質子數=電子數,正負相消</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>原子核小而集中帶正電</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>隨新實驗證據調整,科學暫時性</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>原子核小而集中帶正電</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>原子內部大部分是空的</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
